--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.17303517674213</v>
+        <v>2.465618216220597</v>
       </c>
       <c r="D2" t="n">
-        <v>45.21541380467975</v>
+        <v>7.347504743260459</v>
       </c>
       <c r="E2" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F2" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.96449433433678</v>
+        <v>6.656730329329727</v>
       </c>
       <c r="D3" t="n">
-        <v>30.90198408351123</v>
+        <v>5.021572413570576</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F3" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.24630226898657</v>
+        <v>3.615024118710318</v>
       </c>
       <c r="D4" t="n">
-        <v>14.53013961285502</v>
+        <v>2.361147687088941</v>
       </c>
       <c r="E4" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F4" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.81804806653007</v>
+        <v>5.820432810811136</v>
       </c>
       <c r="D5" t="n">
-        <v>34.81311248324553</v>
+        <v>5.657130778527399</v>
       </c>
       <c r="E5" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F5" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.7895539737961</v>
+        <v>6.628302520741867</v>
       </c>
       <c r="D6" t="n">
-        <v>47.72440030137302</v>
+        <v>7.755215048973115</v>
       </c>
       <c r="E6" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F6" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.58332776107219</v>
+        <v>4.319790761174231</v>
       </c>
       <c r="D7" t="n">
-        <v>18.02554174858286</v>
+        <v>2.929150534144715</v>
       </c>
       <c r="E7" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F7" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.84525908590297</v>
+        <v>8.587354601459232</v>
       </c>
       <c r="D8" t="n">
-        <v>56.77573259991316</v>
+        <v>9.226056547485888</v>
       </c>
       <c r="E8" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F8" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.33418294828023</v>
+        <v>5.741804729095538</v>
       </c>
       <c r="D9" t="n">
-        <v>30.18182355625696</v>
+        <v>4.904546327891756</v>
       </c>
       <c r="E9" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F9" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.212111718715835</v>
+        <v>1.171968154291323</v>
       </c>
       <c r="D10" t="n">
-        <v>33.5282355798882</v>
+        <v>5.448338281731833</v>
       </c>
       <c r="E10" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F10" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.08684150630628</v>
+        <v>5.37661174477477</v>
       </c>
       <c r="D11" t="n">
-        <v>33.00198529558299</v>
+        <v>5.362822610532236</v>
       </c>
       <c r="E11" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F11" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.26290548085899</v>
+        <v>3.617722140639587</v>
       </c>
       <c r="D12" t="n">
-        <v>29.91720319454436</v>
+        <v>4.861545519113458</v>
       </c>
       <c r="E12" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F12" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.61821854113511</v>
+        <v>5.300460512934456</v>
       </c>
       <c r="D13" t="n">
-        <v>57.75297271533967</v>
+        <v>9.384858066242696</v>
       </c>
       <c r="E13" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F13" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.70032838156296</v>
+        <v>7.751303362003982</v>
       </c>
       <c r="D14" t="n">
-        <v>59.78311841957682</v>
+        <v>9.714756743181233</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F14" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.44465908161584</v>
+        <v>6.734757100762574</v>
       </c>
       <c r="D15" t="n">
-        <v>58.92152803368243</v>
+        <v>9.574748305473396</v>
       </c>
       <c r="E15" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F15" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.28826802609805</v>
+        <v>7.034343554240933</v>
       </c>
       <c r="D16" t="n">
-        <v>70.23285411052485</v>
+        <v>11.41283879296029</v>
       </c>
       <c r="E16" t="n">
-        <v>12.05346750781089</v>
+        <v>1.95868847001927</v>
       </c>
       <c r="F16" t="n">
-        <v>16.01416469467451</v>
+        <v>2.602301762884609</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
